--- a/db/templates/invoice_tunisia.xlsx
+++ b/db/templates/invoice_tunisia.xlsx
@@ -401,7 +401,7 @@
     <t>Full "Withholding tax (12%): 40.00 EUR" line, entirely blank (if unset)</t>
   </si>
   <si>
-    <t>Whole "Arrêtée la présente facture à la somme de ..." sentence, blank unless enabled in Formatting settings</t>
+    <t>Whole amount-in-words sentence in the organization's document language (French: "Arrêtée la présente facture à la somme de ..."), blank unless enabled in Formatting settings</t>
   </si>
   <si>
     <t>{{organization.iban}}</t>

--- a/db/templates/invoice_tunisia.xlsx
+++ b/db/templates/invoice_tunisia.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <si>
     <t>{{organization.logo}}</t>
   </si>
@@ -41,244 +41,250 @@
     <t>{{client.name}}</t>
   </si>
   <si>
+    <t>{{client.addressLine}}</t>
+  </si>
+  <si>
+    <t>{{client.postalCode}} {{client.city}}</t>
+  </si>
+  <si>
+    <t>Tel: {{client.phone}}</t>
+  </si>
+  <si>
+    <t>CIN: {{client.identityNumber}}</t>
+  </si>
+  <si>
+    <t>Facture N°: {{invoice.number}}</t>
+  </si>
+  <si>
+    <t>Date : {{invoice.date}}</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Désignation</t>
+  </si>
+  <si>
+    <t>Quantité</t>
+  </si>
+  <si>
+    <t>P.U HT</t>
+  </si>
+  <si>
+    <t>TOTAL HT</t>
+  </si>
+  <si>
+    <t>{{lineItems.sku}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.description}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.quantity}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.unitPrice}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.lineTotal}}</t>
+  </si>
+  <si>
+    <t>{{#lineItems}}</t>
+  </si>
+  <si>
+    <t>Taux TVA %</t>
+  </si>
+  <si>
+    <t>Base TVA</t>
+  </si>
+  <si>
+    <t>Montant TVA</t>
+  </si>
+  <si>
+    <t>{{taxLines.rate}}</t>
+  </si>
+  <si>
+    <t>{{taxLines.base}}</t>
+  </si>
+  <si>
+    <t>{{taxLines.amount}}</t>
+  </si>
+  <si>
+    <t>{{#taxLines}}</t>
+  </si>
+  <si>
+    <t>Total Brut HTVA</t>
+  </si>
+  <si>
+    <t>{{invoice.subTotal}}</t>
+  </si>
+  <si>
+    <t>Remise</t>
+  </si>
+  <si>
+    <t>{{invoice.discountAmount}}</t>
+  </si>
+  <si>
+    <t>Total Net HTVA</t>
+  </si>
+  <si>
+    <t>{{invoice.netTaxable}}</t>
+  </si>
+  <si>
+    <t>Total TVA</t>
+  </si>
+  <si>
+    <t>{{invoice.taxTotal}}</t>
+  </si>
+  <si>
+    <t>D.Timbre</t>
+  </si>
+  <si>
+    <t>{{invoice.fiscalStampAmount}}</t>
+  </si>
+  <si>
+    <t>Total TTC</t>
+  </si>
+  <si>
+    <t>{{invoice.total}}</t>
+  </si>
+  <si>
+    <t>{{invoice.amountInWords}}</t>
+  </si>
+  <si>
+    <t>Cachet et Signature</t>
+  </si>
+  <si>
+    <t>IBAN : {{organization.iban}}</t>
+  </si>
+  <si>
+    <t>{{organization.bankName}}</t>
+  </si>
+  <si>
+    <t>Available template placeholders</t>
+  </si>
+  <si>
+    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Placeholder</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Header</t>
+  </si>
+  <si>
+    <t>Seller logo — place alone in a cell to anchor the uploaded image there (blank if the org has none)</t>
+  </si>
+  <si>
+    <t>{{invoice.number}}</t>
+  </si>
+  <si>
+    <t>Invoice number</t>
+  </si>
+  <si>
+    <t>{{invoice.date}}</t>
+  </si>
+  <si>
+    <t>Invoice date</t>
+  </si>
+  <si>
+    <t>{{invoice.dueDate}}</t>
+  </si>
+  <si>
+    <t>Payment due date</t>
+  </si>
+  <si>
+    <t>{{invoice.currency}}</t>
+  </si>
+  <si>
+    <t>Currency code (e.g. EUR)</t>
+  </si>
+  <si>
+    <t>{{invoice.buyerReference}}</t>
+  </si>
+  <si>
+    <t>Buyer reference (e.g. a Leitweg-ID)</t>
+  </si>
+  <si>
+    <t>Seller company name</t>
+  </si>
+  <si>
+    <t>{{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>Seller VAT / MF number</t>
+  </si>
+  <si>
+    <t>{{organization.email}}</t>
+  </si>
+  <si>
+    <t>Seller email</t>
+  </si>
+  <si>
+    <t>{{organization.phone}}</t>
+  </si>
+  <si>
+    <t>Seller phone</t>
+  </si>
+  <si>
+    <t>{{organization.website}}</t>
+  </si>
+  <si>
+    <t>Seller website</t>
+  </si>
+  <si>
+    <t>{{organization.street}}</t>
+  </si>
+  <si>
+    <t>Seller street</t>
+  </si>
+  <si>
+    <t>{{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Seller house number</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}}</t>
+  </si>
+  <si>
+    <t>Seller postal code</t>
+  </si>
+  <si>
+    <t>{{organization.city}}</t>
+  </si>
+  <si>
+    <t>Seller city</t>
+  </si>
+  <si>
+    <t>Customer name</t>
+  </si>
+  <si>
+    <t>{{client.vatin}}</t>
+  </si>
+  <si>
+    <t>Customer VAT / MF number</t>
+  </si>
+  <si>
+    <t>{{client.identityNumber}}</t>
+  </si>
+  <si>
+    <t>Customer national ID / CIN number</t>
+  </si>
+  <si>
     <t>{{client.address}}</t>
   </si>
   <si>
-    <t>{{client.postalCode}} {{client.city}}</t>
-  </si>
-  <si>
-    <t>Tel: {{client.phone}}</t>
-  </si>
-  <si>
-    <t>CIN: {{client.identityNumber}}</t>
-  </si>
-  <si>
-    <t>Facture N°: {{invoice.number}}</t>
-  </si>
-  <si>
-    <t>Date : {{invoice.date}}</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Désignation</t>
-  </si>
-  <si>
-    <t>Quantité</t>
-  </si>
-  <si>
-    <t>P.U HT</t>
-  </si>
-  <si>
-    <t>TOTAL HT</t>
-  </si>
-  <si>
-    <t>{{lineItems.sku}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.description}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.quantity}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.unitPrice}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.lineTotal}}</t>
-  </si>
-  <si>
-    <t>{{#lineItems}}</t>
-  </si>
-  <si>
-    <t>Taux TVA %</t>
-  </si>
-  <si>
-    <t>Base TVA</t>
-  </si>
-  <si>
-    <t>Montant TVA</t>
-  </si>
-  <si>
-    <t>{{taxLines.rate}}</t>
-  </si>
-  <si>
-    <t>{{taxLines.base}}</t>
-  </si>
-  <si>
-    <t>{{taxLines.amount}}</t>
-  </si>
-  <si>
-    <t>{{#taxLines}}</t>
-  </si>
-  <si>
-    <t>Total Brut HTVA</t>
-  </si>
-  <si>
-    <t>{{invoice.subTotal}}</t>
-  </si>
-  <si>
-    <t>Remise</t>
-  </si>
-  <si>
-    <t>{{invoice.discountAmount}}</t>
-  </si>
-  <si>
-    <t>Total Net HTVA</t>
-  </si>
-  <si>
-    <t>{{invoice.netTaxable}}</t>
-  </si>
-  <si>
-    <t>Total TVA</t>
-  </si>
-  <si>
-    <t>{{invoice.taxTotal}}</t>
-  </si>
-  <si>
-    <t>D.Timbre</t>
-  </si>
-  <si>
-    <t>{{invoice.fiscalStampAmount}}</t>
-  </si>
-  <si>
-    <t>Total TTC</t>
-  </si>
-  <si>
-    <t>{{invoice.total}}</t>
-  </si>
-  <si>
-    <t>{{invoice.amountInWords}}</t>
-  </si>
-  <si>
-    <t>Cachet et Signature</t>
-  </si>
-  <si>
-    <t>IBAN : {{organization.iban}}</t>
-  </si>
-  <si>
-    <t>{{organization.bankName}}</t>
-  </si>
-  <si>
-    <t>Available template placeholders</t>
-  </si>
-  <si>
-    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Placeholder</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Header</t>
-  </si>
-  <si>
-    <t>Seller logo — place alone in a cell to anchor the uploaded image there (blank if the org has none)</t>
-  </si>
-  <si>
-    <t>{{invoice.number}}</t>
-  </si>
-  <si>
-    <t>Invoice number</t>
-  </si>
-  <si>
-    <t>{{invoice.date}}</t>
-  </si>
-  <si>
-    <t>Invoice date</t>
-  </si>
-  <si>
-    <t>{{invoice.dueDate}}</t>
-  </si>
-  <si>
-    <t>Payment due date</t>
-  </si>
-  <si>
-    <t>{{invoice.currency}}</t>
-  </si>
-  <si>
-    <t>Currency code (e.g. EUR)</t>
-  </si>
-  <si>
-    <t>{{invoice.buyerReference}}</t>
-  </si>
-  <si>
-    <t>Buyer reference (e.g. a Leitweg-ID)</t>
-  </si>
-  <si>
-    <t>Seller company name</t>
-  </si>
-  <si>
-    <t>{{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>Seller VAT / MF number</t>
-  </si>
-  <si>
-    <t>{{organization.email}}</t>
-  </si>
-  <si>
-    <t>Seller email</t>
-  </si>
-  <si>
-    <t>{{organization.phone}}</t>
-  </si>
-  <si>
-    <t>Seller phone</t>
-  </si>
-  <si>
-    <t>{{organization.website}}</t>
-  </si>
-  <si>
-    <t>Seller website</t>
-  </si>
-  <si>
-    <t>{{organization.street}}</t>
-  </si>
-  <si>
-    <t>Seller street</t>
-  </si>
-  <si>
-    <t>{{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Seller house number</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}}</t>
-  </si>
-  <si>
-    <t>Seller postal code</t>
-  </si>
-  <si>
-    <t>{{organization.city}}</t>
-  </si>
-  <si>
-    <t>Seller city</t>
-  </si>
-  <si>
-    <t>Customer name</t>
-  </si>
-  <si>
-    <t>{{client.vatin}}</t>
-  </si>
-  <si>
-    <t>Customer VAT / MF number</t>
-  </si>
-  <si>
-    <t>{{client.identityNumber}}</t>
-  </si>
-  <si>
-    <t>Customer national ID / CIN number</t>
-  </si>
-  <si>
     <t>Customer single-line address</t>
+  </si>
+  <si>
+    <t>Customer street and house number, or the single-line address when there is no street</t>
   </si>
   <si>
     <t>{{client.email}}</t>
@@ -1248,15 +1254,15 @@
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="C25" t="s">
         <v>88</v>
@@ -1319,53 +1325,53 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="s">
+      <c r="B33" t="s">
         <v>103</v>
       </c>
+      <c r="C33" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="34">
-      <c r="B34" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" t="s">
-        <v>104</v>
+      <c r="A34" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="s">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="C39" t="s">
         <v>110</v>
@@ -1373,97 +1379,97 @@
     </row>
     <row r="40">
       <c r="B40" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="s">
         <v>22</v>
       </c>
-      <c r="C40" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="s">
-        <v>112</v>
+      <c r="C41" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="s">
-        <v>30</v>
-      </c>
-      <c r="C42" t="s">
-        <v>113</v>
+      <c r="A42" s="11" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="s">
         <v>29</v>
       </c>
-      <c r="C45" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="11" t="s">
-        <v>117</v>
+      <c r="C46" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47" t="s">
-        <v>118</v>
+      <c r="A47" s="11" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C49" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C50" t="s">
-        <v>37</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C51" t="s">
-        <v>121</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="C52" t="s">
         <v>123</v>
@@ -1471,15 +1477,15 @@
     </row>
     <row r="53">
       <c r="B53" t="s">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="C53" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="s">
-        <v>125</v>
+        <v>40</v>
       </c>
       <c r="C54" t="s">
         <v>126</v>
@@ -1487,15 +1493,15 @@
     </row>
     <row r="55">
       <c r="B55" t="s">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="C55" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="s">
-        <v>128</v>
+        <v>43</v>
       </c>
       <c r="C56" t="s">
         <v>129</v>
@@ -1503,22 +1509,22 @@
     </row>
     <row r="57">
       <c r="B57" t="s">
+        <v>130</v>
+      </c>
+      <c r="C57" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="s">
         <v>46</v>
       </c>
-      <c r="C57" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="s">
-        <v>131</v>
+      <c r="C58" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="s">
-        <v>132</v>
-      </c>
-      <c r="C59" t="s">
+      <c r="A59" s="11" t="s">
         <v>133</v>
       </c>
     </row>
@@ -1536,16 +1542,24 @@
       </c>
       <c r="C61" t="s">
         <v>137</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="s">
+        <v>138</v>
+      </c>
+      <c r="C62" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A59:C59"/>
   </mergeCells>
 </worksheet>
 </file>